--- a/荷量実績_20241030-20241106.xlsx
+++ b/荷量実績_20241030-20241106.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>項目名</t>
   </si>
@@ -34,7 +34,7 @@
     <t>選択された便</t>
   </si>
   <si>
-    <t>8t常傭便3_2</t>
+    <t>8t常傭便1_1</t>
   </si>
   <si>
     <t>便名称</t>
@@ -79,43 +79,115 @@
     <t>出発荷量画像パス</t>
   </si>
   <si>
-    <t>8t常傭便3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>名城</t>
-  </si>
-  <si>
-    <t>2160</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>2024/11/06</t>
-  </si>
-  <si>
-    <t>2024/11/06 09:55</t>
-  </si>
-  <si>
-    <t>2024/11/06 10:08</t>
-  </si>
-  <si>
-    <t>81-90</t>
+    <t>8t常傭便1</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>岩渕</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>2024/10/30</t>
+  </si>
+  <si>
+    <t>2024/10/30 16:47</t>
+  </si>
+  <si>
+    <t>2024/10/30 17:00</t>
+  </si>
+  <si>
+    <t>51-60</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-10-30\51-60%\image_2024-10-30_16z47z49.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-10-30\0%\image_2024-10-30_17z00z07.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/31</t>
+  </si>
+  <si>
+    <t>2024/10/31 17:00</t>
+  </si>
+  <si>
+    <t>2024/10/31 17:03</t>
+  </si>
+  <si>
+    <t>61-70</t>
   </si>
   <si>
     <t>1-10</t>
   </si>
   <si>
-    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\2\img\2024-11-06\81-90%\image_2024-11-06_09z55z46.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\2\img\2024-11-06\1-10%\image_2024-11-06_10z08z41.jpg</t>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-10-31\61-70%\image_2024-10-31_16z48z58.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-10-31\1-10%\image_2024-10-31_17z03z28.jpg</t>
+  </si>
+  <si>
+    <t>2024/11/01</t>
+  </si>
+  <si>
+    <t>2024/11/01 16:51</t>
+  </si>
+  <si>
+    <t>2024/11/01 17:05</t>
+  </si>
+  <si>
+    <t>41-50</t>
+  </si>
+  <si>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-11-01\41-50%\image_2024-11-01_16z51z54.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-11-01\1-10%\image_2024-11-01_17z05z03.jpg</t>
+  </si>
+  <si>
+    <t>2024/11/04</t>
+  </si>
+  <si>
+    <t>2024/11/04 16:51</t>
+  </si>
+  <si>
+    <t>2024/11/04 17:01</t>
+  </si>
+  <si>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-11-04\51-60%\image_2024-11-04_16z51z38.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-11-04\0%\image_2024-11-04_17z01z23.jpg</t>
+  </si>
+  <si>
+    <t>2024/11/05</t>
+  </si>
+  <si>
+    <t>2024/11/05 16:44</t>
+  </si>
+  <si>
+    <t>2024/11/05 16:54</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-11-05\41-50%\image_2024-11-05_16z44z28.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.46\share\AI-truck-load-detect\syncbace\1\img\2024-11-05\1-10%\image_2024-11-05_16z54z06.jpg</t>
   </si>
 </sst>
 </file>
@@ -198,7 +270,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -259,7 +331,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="0" t="s">
         <v>23</v>
@@ -293,6 +365,194 @@
       </c>
       <c r="O2" s="0" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="0">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="O6" s="0" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
